--- a/etf_holdings/2026-08-21_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:14</t>
+          <t>2026-08-21 14:41:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.06%2375</t>
+          <t>+1.47%2410</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2375</v>
+        <v>2410</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:14</t>
+          <t>2026-08-21 14:41:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.79%5985</t>
+          <t>-5.1%5680</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5985</v>
+        <v>5680</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:14</t>
+          <t>2026-08-21 14:41:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+7.48%517</t>
+          <t>+2.13%528</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+7.48%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:14</t>
+          <t>2026-08-21 14:41:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-1.21%13925</t>
+          <t>-3.88%13385</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-3.88%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>13925</v>
+        <v>13385</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:14</t>
+          <t>2026-08-21 14:41:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.88%1140</t>
+          <t>-4.82%1085</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-4.82%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1140</v>
+        <v>1085</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:14</t>
+          <t>2026-08-21 14:41:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-2.43%562</t>
+          <t>-1.42%554</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:14</t>
+          <t>2026-08-21 14:41:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+1.27%1195</t>
+          <t>-5.02%1135</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+1.27%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1195</v>
+        <v>1135</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:14</t>
+          <t>2026-08-21 14:41:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.78%6325</t>
+          <t>-1.11%6255</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6325</v>
+        <v>6255</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:14</t>
+          <t>2026-08-21 14:41:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.94%2105</t>
+          <t>-3.33%2035</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2105</v>
+        <v>2035</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:14</t>
+          <t>2026-08-21 14:41:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+5%1575</t>
+          <t>-5.08%1495</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+5%</t>
+          <t>-5.08%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1575</v>
+        <v>1495</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:14</t>
+          <t>2026-08-21 14:41:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-3.55%2985</t>
+          <t>-4.02%2865</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.55%</t>
+          <t>-4.02%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2985</v>
+        <v>2865</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:14</t>
+          <t>2026-08-21 14:41:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+7.52%5650</t>
+          <t>-3.27%5465</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+7.52%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5650</v>
+        <v>5465</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:14</t>
+          <t>2026-08-21 14:41:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-3.77%3700</t>
+          <t>+2.43%3790</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.77%</t>
+          <t>+2.43%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3700</v>
+        <v>3790</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:14</t>
+          <t>2026-08-21 14:41:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.24%851</t>
+          <t>-4.7%811</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>851</v>
+        <v>811</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:14</t>
+          <t>2026-08-21 14:41:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.16%6455</t>
+          <t>-0.77%6405</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6455</v>
+        <v>6405</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:15</t>
+          <t>2026-08-21 14:41:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+3.73%2780</t>
+          <t>+5.04%2920</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+3.73%</t>
+          <t>+5.04%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2780</v>
+        <v>2920</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:15</t>
+          <t>2026-08-21 14:41:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+2.9%710</t>
+          <t>-10%639</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>710</v>
+        <v>639</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:15</t>
+          <t>2026-08-21 14:41:12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+2.56%5600</t>
+          <t>-3.66%5395</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>-3.66%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5600</v>
+        <v>5395</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:15</t>
+          <t>2026-08-21 14:41:12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.51%15750</t>
+          <t>-2.54%15350</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>15750</v>
+        <v>15350</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:15</t>
+          <t>2026-08-21 14:41:12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+1.53%1995</t>
+          <t>+4.01%2075</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+4.01%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1995</v>
+        <v>2075</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:15</t>
+          <t>2026-08-21 14:41:12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.63%5515</t>
+          <t>+1.72%5610</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5515</v>
+        <v>5610</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:15</t>
+          <t>2026-08-21 14:41:12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.34%590</t>
+          <t>-0.51%587</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:15</t>
+          <t>2026-08-21 14:41:12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.21%327</t>
+          <t>-1.68%321.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>327</v>
+        <v>321.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:15</t>
+          <t>2026-08-21 14:41:12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.61%246.5</t>
+          <t>-0.41%245.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>246.5</v>
+        <v>245.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:15</t>
+          <t>2026-08-21 14:41:12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+2.29%246</t>
+          <t>+2.24%251.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>246</v>
+        <v>251.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:15</t>
+          <t>2026-08-21 14:41:12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+2.27%2250</t>
+          <t>+1.11%2275</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2250</v>
+        <v>2275</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:15</t>
+          <t>2026-08-21 14:41:12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.94%2140</t>
+          <t>-1.87%2100</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2140</v>
+        <v>2100</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:15</t>
+          <t>2026-08-21 14:41:12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.13%1745</t>
+          <t>+0.29%1750</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1745</v>
+        <v>1750</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:15</t>
+          <t>2026-08-21 14:41:12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.1%180</t>
+          <t>-2.5%175.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>180</v>
+        <v>175.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:15</t>
+          <t>2026-08-21 14:41:12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+1.32%153.5</t>
+          <t>-1.3%151.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>153.5</v>
+        <v>151.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:17</t>
+          <t>2026-08-21 14:41:14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.39%128</t>
+          <t>+4.69%134</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+4.69%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:17</t>
+          <t>2026-08-21 14:41:14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.83%1075</t>
+          <t>-1.4%1060</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.83%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1075</v>
+        <v>1060</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:17</t>
+          <t>2026-08-21 14:41:14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.3%913</t>
+          <t>+0.88%921</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:17</t>
+          <t>2026-08-21 14:41:14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.61%97.7</t>
+          <t>+2.87%100.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>+2.87%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>97.7</v>
+        <v>100.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:17</t>
+          <t>2026-08-21 14:41:14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.74%703</t>
+          <t>+1.56%714</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.74%</t>
+          <t>+1.56%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:17</t>
+          <t>2026-08-21 14:41:14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-0.64%62.1</t>
+          <t>+3.06%64</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>+3.06%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>62.1</v>
+        <v>64</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:17</t>
+          <t>2026-08-21 14:41:14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.31%63.4</t>
+          <t>+2.52%65</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>+2.52%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>63.4</v>
+        <v>65</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:17</t>
+          <t>2026-08-21 14:41:14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1.04%485.5</t>
+          <t>-5.46%459</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-5.46%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>485.5</v>
+        <v>459</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:17</t>
+          <t>2026-08-21 14:41:14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.13%39.35</t>
+          <t>+0.64%39.6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>39.35</v>
+        <v>39.6</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:17</t>
+          <t>2026-08-21 14:41:14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.38%46.4</t>
+          <t>+1.19%46.95</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>+1.19%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>46.4</v>
+        <v>46.95</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:17</t>
+          <t>2026-08-21 14:41:14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.51%38.8</t>
+          <t>+2.06%39.6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>+2.06%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>38.8</v>
+        <v>39.6</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:17</t>
+          <t>2026-08-21 14:41:14</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.24%35.95</t>
+          <t>+3.62%37.25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+3.62%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>35.95</v>
+        <v>37.25</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:17</t>
+          <t>2026-08-21 14:41:14</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0%30.4</t>
+          <t>+3.78%31.55</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>30.4</v>
+        <v>31.55</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:17</t>
+          <t>2026-08-21 14:41:14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.19%37.35</t>
+          <t>+1.74%38</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>37.35</v>
+        <v>38</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:17</t>
+          <t>2026-08-21 14:41:14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0%235</t>
+          <t>-1.28%232</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:18</t>
+          <t>2026-08-21 14:41:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+4.82%217.5</t>
+          <t>-1.84%213.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+4.82%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>217.5</v>
+        <v>213.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:18</t>
+          <t>2026-08-21 14:41:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.69%220</t>
+          <t>+1.59%223.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+1.59%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>220</v>
+        <v>223.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:18</t>
+          <t>2026-08-21 14:41:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+1.99%205.5</t>
+          <t>+0.24%206</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>205.5</v>
+        <v>206</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:18</t>
+          <t>2026-08-21 14:41:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+0.37%136.5</t>
+          <t>0%136.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 08:46:18</t>
+          <t>2026-08-21 14:41:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.9%78.2</t>
+          <t>-0.9%77.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>78.2</v>
+        <v>77.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-08-21_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:11</t>
+          <t>2026-08-21 14:54:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:11</t>
+          <t>2026-08-21 14:54:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:11</t>
+          <t>2026-08-21 14:54:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:11</t>
+          <t>2026-08-21 14:54:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:11</t>
+          <t>2026-08-21 14:54:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:11</t>
+          <t>2026-08-21 14:54:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:11</t>
+          <t>2026-08-21 14:54:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:11</t>
+          <t>2026-08-21 14:54:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:11</t>
+          <t>2026-08-21 14:54:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:11</t>
+          <t>2026-08-21 14:54:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:11</t>
+          <t>2026-08-21 14:54:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:11</t>
+          <t>2026-08-21 14:54:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:11</t>
+          <t>2026-08-21 14:54:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:11</t>
+          <t>2026-08-21 14:54:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:11</t>
+          <t>2026-08-21 14:54:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:12</t>
+          <t>2026-08-21 14:54:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:12</t>
+          <t>2026-08-21 14:54:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:12</t>
+          <t>2026-08-21 14:54:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:12</t>
+          <t>2026-08-21 14:54:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:12</t>
+          <t>2026-08-21 14:54:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:12</t>
+          <t>2026-08-21 14:54:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:12</t>
+          <t>2026-08-21 14:54:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:12</t>
+          <t>2026-08-21 14:54:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:12</t>
+          <t>2026-08-21 14:54:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:12</t>
+          <t>2026-08-21 14:54:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:12</t>
+          <t>2026-08-21 14:54:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:12</t>
+          <t>2026-08-21 14:54:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:12</t>
+          <t>2026-08-21 14:54:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:12</t>
+          <t>2026-08-21 14:54:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:12</t>
+          <t>2026-08-21 14:54:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:14</t>
+          <t>2026-08-21 14:54:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:14</t>
+          <t>2026-08-21 14:54:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:14</t>
+          <t>2026-08-21 14:54:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:14</t>
+          <t>2026-08-21 14:54:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:14</t>
+          <t>2026-08-21 14:54:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:14</t>
+          <t>2026-08-21 14:54:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:14</t>
+          <t>2026-08-21 14:54:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:14</t>
+          <t>2026-08-21 14:54:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:14</t>
+          <t>2026-08-21 14:54:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:14</t>
+          <t>2026-08-21 14:54:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:14</t>
+          <t>2026-08-21 14:54:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:14</t>
+          <t>2026-08-21 14:54:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:14</t>
+          <t>2026-08-21 14:54:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:14</t>
+          <t>2026-08-21 14:54:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:14</t>
+          <t>2026-08-21 14:54:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:15</t>
+          <t>2026-08-21 14:54:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:15</t>
+          <t>2026-08-21 14:54:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:15</t>
+          <t>2026-08-21 14:54:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:15</t>
+          <t>2026-08-21 14:54:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 14:41:15</t>
+          <t>2026-08-21 14:54:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:29</t>
+          <t>2026-08-21 16:06:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:30</t>
+          <t>2026-08-21 16:07:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:31</t>
+          <t>2026-08-21 16:07:01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:32</t>
+          <t>2026-08-21 16:07:02</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:32</t>
+          <t>2026-08-21 16:07:02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:32</t>
+          <t>2026-08-21 16:07:02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:32</t>
+          <t>2026-08-21 16:07:02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:32</t>
+          <t>2026-08-21 16:07:02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:06:58</t>
+          <t>2026-08-21 16:24:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:00</t>
+          <t>2026-08-21 16:24:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:01</t>
+          <t>2026-08-21 16:24:55</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:02</t>
+          <t>2026-08-21 16:24:56</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:02</t>
+          <t>2026-08-21 16:24:56</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:02</t>
+          <t>2026-08-21 16:24:56</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:02</t>
+          <t>2026-08-21 16:24:56</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:02</t>
+          <t>2026-08-21 16:24:56</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:52</t>
+          <t>2026-08-21 16:40:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:54</t>
+          <t>2026-08-21 16:40:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:55</t>
+          <t>2026-08-21 16:40:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:56</t>
+          <t>2026-08-21 16:40:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:56</t>
+          <t>2026-08-21 16:40:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:56</t>
+          <t>2026-08-21 16:40:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:56</t>
+          <t>2026-08-21 16:40:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:24:56</t>
+          <t>2026-08-21 16:40:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:37</t>
+          <t>2026-08-21 20:04:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12.29%4,500,000</t>
+          <t>12.80%4,500,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12.29%</t>
+          <t>12.80%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:37</t>
+          <t>2026-08-21 20:04:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,20 +583,20 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.84%1,430,000</t>
+          <t>9.38%1,400,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.84%</t>
+          <t>9.38%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1430000</v>
+        <v>1400000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:37</t>
+          <t>2026-08-21 20:04:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.32%14,000,000</t>
+          <t>8.72%14,000,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.32%</t>
+          <t>8.72%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:37</t>
+          <t>2026-08-21 20:04:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.17%510,000</t>
+          <t>8.05%510,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.17%</t>
+          <t>8.05%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:37</t>
+          <t>2026-08-21 20:04:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.55%5,000,000</t>
+          <t>6.40%5,000,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.55%</t>
+          <t>6.40%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:37</t>
+          <t>2026-08-21 20:04:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.98%7,700,000</t>
+          <t>5.03%7,700,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.98%</t>
+          <t>5.03%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:37</t>
+          <t>2026-08-21 20:04:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,25 +870,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8046南亞電路</t>
+          <t>2454聯發科技</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-5.02%1135</t>
+          <t>+2.43%3790</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.02%</t>
+          <t>+2.43%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1135</v>
+        <v>3790</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.47%3,250,000</t>
+          <t>4.47%1,000,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -897,11 +897,11 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3250000</v>
+        <v>1000000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:37</t>
+          <t>2026-08-21 20:04:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.36%600,000</t>
+          <t>4.43%600,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.36%</t>
+          <t>4.43%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:37</t>
+          <t>2026-08-21 20:04:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2345智邦科技</t>
+          <t>8046南亞電路</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.33%2035</t>
+          <t>-5.02%1135</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2035</v>
+        <v>1135</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.36%1,800,000</t>
+          <t>4.35%3,250,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.36%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1800000</v>
+        <v>3250000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:37</t>
+          <t>2026-08-21 20:04:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6274台燿科技</t>
+          <t>6223旺矽科技</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-5.08%1495</t>
+          <t>-3.27%5465</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.08%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1495</v>
+        <v>5465</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.35%2,400,000</t>
+          <t>4.26%660,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>4.26%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2400000</v>
+        <v>660000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:37</t>
+          <t>2026-08-21 20:04:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3017奇鋐科技</t>
+          <t>6274台燿科技</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-4.02%2865</t>
+          <t>-5.08%1495</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-4.02%</t>
+          <t>-5.08%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2865</v>
+        <v>1495</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.29%1,250,000</t>
+          <t>4.23%2,400,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.29%</t>
+          <t>4.23%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1250000</v>
+        <v>2400000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:37</t>
+          <t>2026-08-21 20:04:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6223旺矽科技</t>
+          <t>3017奇鋐科技</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.27%5465</t>
+          <t>-4.02%2865</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.27%</t>
+          <t>-4.02%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5465</v>
+        <v>2865</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.29%660,000</t>
+          <t>4.23%1,250,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.29%</t>
+          <t>4.23%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>660000</v>
+        <v>1250000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:37</t>
+          <t>2026-08-21 20:04:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2454聯發科技</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+2.43%3790</t>
+          <t>-3.33%2035</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+2.43%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3790</v>
+        <v>2035</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.25%1,000,000</t>
+          <t>4.20%1,750,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>4.20%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1000000</v>
+        <v>1750000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:37</t>
+          <t>2026-08-21 20:04:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.01%4,100,000</t>
+          <t>3.92%4,100,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:37</t>
+          <t>2026-08-21 20:04:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,16 +1376,16 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.97%400,000</t>
+          <t>2.87%380,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>400000</v>
+        <v>380000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:39</t>
+          <t>2026-08-21 20:04:11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.24%700,000</t>
+          <t>2.41%700,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:39</t>
+          <t>2026-08-21 20:04:11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3026禾伸堂企</t>
+          <t>5274信驊科技</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-10%639</t>
+          <t>-2.54%15350</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>639</v>
+        <v>15350</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.21%2,700,000</t>
+          <t>2.18%120,500</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.18%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2700000</v>
+        <v>120500</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:39</t>
+          <t>2026-08-21 20:04:11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.19%340,000</t>
+          <t>2.16%340,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:39</t>
+          <t>2026-08-21 20:04:11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5274信驊科技</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.54%15350</t>
+          <t>+4.01%2075</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.54%</t>
+          <t>+4.01%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>15350</v>
+        <v>2075</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.18%120,500</t>
+          <t>2.15%880,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>120500</v>
+        <v>880000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:39</t>
+          <t>2026-08-21 20:04:11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>3026禾伸堂企</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+4.01%2075</t>
+          <t>-10%639</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+4.01%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2075</v>
+        <v>639</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.02%880,000</t>
+          <t>2.04%2,700,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>880000</v>
+        <v>2700000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:39</t>
+          <t>2026-08-21 20:04:11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:39</t>
+          <t>2026-08-21 20:04:11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:39</t>
+          <t>2026-08-21 20:04:11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:39</t>
+          <t>2026-08-21 20:04:11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:39</t>
+          <t>2026-08-21 20:04:11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:39</t>
+          <t>2026-08-21 20:04:11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:39</t>
+          <t>2026-08-21 20:04:11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:39</t>
+          <t>2026-08-21 20:04:11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:39</t>
+          <t>2026-08-21 20:04:11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:39</t>
+          <t>2026-08-21 20:04:11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:40</t>
+          <t>2026-08-21 20:04:12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:40</t>
+          <t>2026-08-21 20:04:12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:40</t>
+          <t>2026-08-21 20:04:12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:40</t>
+          <t>2026-08-21 20:04:12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:40</t>
+          <t>2026-08-21 20:04:12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:40</t>
+          <t>2026-08-21 20:04:12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:40</t>
+          <t>2026-08-21 20:04:12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:40</t>
+          <t>2026-08-21 20:04:12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:40</t>
+          <t>2026-08-21 20:04:12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:40</t>
+          <t>2026-08-21 20:04:12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:40</t>
+          <t>2026-08-21 20:04:12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,25 +2944,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2880華南金融</t>
+          <t>2884玉山金融</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+2.06%39.6</t>
+          <t>+1.74%38</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+2.06%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>39.6</v>
+        <v>38</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0%9,090</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>9090</v>
+        <v>9000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:40</t>
+          <t>2026-08-21 20:04:12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2887台新新光</t>
+          <t>2880華南金融</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+3.62%37.25</t>
+          <t>+2.06%39.6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+3.62%</t>
+          <t>+2.06%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>37.25</v>
+        <v>39.6</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%9,090</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>9000</v>
+        <v>9090</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:40</t>
+          <t>2026-08-21 20:04:12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:40</t>
+          <t>2026-08-21 20:04:12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2884玉山金融</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.74%38</t>
+          <t>-1.28%232</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.74%</t>
+          <t>-1.28%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%1,450</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>9000</v>
+        <v>1450</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:40</t>
+          <t>2026-08-21 20:04:12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>2887台新新光</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.28%232</t>
+          <t>+3.62%37.25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.28%</t>
+          <t>+3.62%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>232</v>
+        <v>37.25</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0%1,450</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1450</v>
+        <v>9000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:41</t>
+          <t>2026-08-21 20:04:13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:41</t>
+          <t>2026-08-21 20:04:13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:41</t>
+          <t>2026-08-21 20:04:13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:41</t>
+          <t>2026-08-21 20:04:13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:40:41</t>
+          <t>2026-08-21 20:04:13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
